--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFCECBD-E78D-2148-9745-C3B4AD9F93BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C542E4-BCA2-F049-BB7A-910E05581693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1040" windowWidth="38400" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1300,6 +1300,12 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
       <c r="D6" t="s">
         <v>7</v>
       </c>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C542E4-BCA2-F049-BB7A-910E05581693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73B5AF5-C12C-D04C-9496-C27076CFA122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1040" windowWidth="38400" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1258,6 +1258,12 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73B5AF5-C12C-D04C-9496-C27076CFA122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6523FB04-BEC1-3141-B210-3BB516629F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1040" windowWidth="38400" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1278,6 +1278,12 @@
       <c r="A4" t="s">
         <v>18</v>
       </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
@@ -1292,6 +1298,12 @@
       <c r="A5" t="s">
         <v>13</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
@@ -1326,6 +1338,12 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
@@ -1340,6 +1358,12 @@
       <c r="A8" t="s">
         <v>23</v>
       </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
       <c r="D8" t="s">
         <v>25</v>
       </c>
@@ -1354,6 +1378,12 @@
       <c r="A9" t="s">
         <v>28</v>
       </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
       <c r="D9" t="s">
         <v>30</v>
       </c>
@@ -1368,6 +1398,12 @@
       <c r="A10" t="s">
         <v>16</v>
       </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
@@ -1382,6 +1418,12 @@
       <c r="A11" t="s">
         <v>21</v>
       </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
       <c r="D11" t="s">
         <v>22</v>
       </c>
@@ -1452,6 +1494,12 @@
       <c r="A16" t="s">
         <v>26</v>
       </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
@@ -1465,6 +1513,12 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6523FB04-BEC1-3141-B210-3BB516629F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA5343B-107A-C44A-A9CF-FDD17A1A9EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1040" windowWidth="38400" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1438,6 +1438,12 @@
       <c r="A12" t="s">
         <v>33</v>
       </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
         <v>35</v>
       </c>
@@ -1452,6 +1458,12 @@
       <c r="A13" t="s">
         <v>38</v>
       </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
       <c r="D13" t="s">
         <v>40</v>
       </c>
@@ -1562,6 +1574,12 @@
       <c r="A20" t="s">
         <v>36</v>
       </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
       <c r="D20" t="s">
         <v>37</v>
       </c>
@@ -1575,6 +1593,12 @@
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>41</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
       </c>
       <c r="D21" t="s">
         <v>42</v>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA5343B-107A-C44A-A9CF-FDD17A1A9EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D6C9A-6D37-624B-A162-04A4C414AA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1040" windowWidth="38400" windowHeight="17440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="teams" sheetId="1" r:id="rId1"/>
@@ -1478,6 +1478,12 @@
       <c r="A14" t="s">
         <v>43</v>
       </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
       <c r="D14" t="s">
         <v>45</v>
       </c>
@@ -1492,6 +1498,12 @@
       <c r="A15" t="s">
         <v>48</v>
       </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
       <c r="D15" t="s">
         <v>50</v>
       </c>
@@ -1546,6 +1558,12 @@
       <c r="A18" t="s">
         <v>53</v>
       </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
       <c r="D18" t="s">
         <v>55</v>
       </c>
@@ -1560,6 +1578,12 @@
       <c r="A19" t="s">
         <v>58</v>
       </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
       <c r="D19" t="s">
         <v>60</v>
       </c>
@@ -1614,6 +1638,12 @@
       <c r="A22" t="s">
         <v>46</v>
       </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
       <c r="D22" t="s">
         <v>47</v>
       </c>
@@ -1628,6 +1658,12 @@
       <c r="A23" t="s">
         <v>51</v>
       </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
       <c r="D23" t="s">
         <v>52</v>
       </c>
@@ -1642,6 +1678,12 @@
       <c r="A24" t="s">
         <v>56</v>
       </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
       <c r="D24" t="s">
         <v>57</v>
       </c>
@@ -1656,6 +1698,12 @@
       <c r="A25" t="s">
         <v>61</v>
       </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
       <c r="D25" t="s">
         <v>62</v>
       </c>
@@ -1670,6 +1718,12 @@
       <c r="A26" t="s">
         <v>3</v>
       </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
       <c r="D26" t="s">
         <v>6</v>
       </c>
@@ -1684,6 +1738,12 @@
       <c r="A27" t="s">
         <v>8</v>
       </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
@@ -1698,6 +1758,12 @@
       <c r="A28" t="s">
         <v>18</v>
       </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
       <c r="D28" t="s">
         <v>21</v>
       </c>
@@ -1712,6 +1778,12 @@
       <c r="A29" t="s">
         <v>5</v>
       </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
       <c r="D29" t="s">
         <v>7</v>
       </c>
@@ -1725,6 +1797,12 @@
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>10</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D6C9A-6D37-624B-A162-04A4C414AA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE8B445-BDE0-1F42-B24F-CCEEF73DC9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1818,6 +1818,12 @@
       <c r="A31" t="s">
         <v>13</v>
       </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
       <c r="D31" t="s">
         <v>16</v>
       </c>
@@ -1832,6 +1838,12 @@
       <c r="A32" t="s">
         <v>20</v>
       </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
       <c r="D32" t="s">
         <v>22</v>
       </c>
@@ -1846,6 +1858,12 @@
       <c r="A33" t="s">
         <v>15</v>
       </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
       <c r="D33" t="s">
         <v>17</v>
       </c>
@@ -1873,6 +1891,12 @@
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>28</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
       </c>
       <c r="D35" t="s">
         <v>31</v>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE8B445-BDE0-1F42-B24F-CCEEF73DC9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112790EA-773A-3144-A1F6-E59039B6E09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1878,6 +1878,12 @@
       <c r="A34" t="s">
         <v>23</v>
       </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
       <c r="D34" t="s">
         <v>26</v>
       </c>
@@ -1912,6 +1918,12 @@
       <c r="A36" t="s">
         <v>25</v>
       </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
       <c r="D36" t="s">
         <v>27</v>
       </c>
@@ -1926,6 +1938,12 @@
       <c r="A37" t="s">
         <v>30</v>
       </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
       <c r="D37" t="s">
         <v>32</v>
       </c>
@@ -1940,6 +1958,12 @@
       <c r="A38" t="s">
         <v>33</v>
       </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
       <c r="D38" t="s">
         <v>36</v>
       </c>
@@ -1954,6 +1978,12 @@
       <c r="A39" t="s">
         <v>38</v>
       </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
       <c r="D39" t="s">
         <v>41</v>
       </c>
@@ -1996,6 +2026,12 @@
       <c r="A42" t="s">
         <v>35</v>
       </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
       <c r="D42" t="s">
         <v>37</v>
       </c>
@@ -2009,6 +2045,12 @@
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>40</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
       </c>
       <c r="D43" t="s">
         <v>42</v>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112790EA-773A-3144-A1F6-E59039B6E09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9B06ED-5A53-574D-A7F5-88BFFAF0C326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1998,6 +1998,12 @@
       <c r="A40" t="s">
         <v>43</v>
       </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
       <c r="D40" t="s">
         <v>46</v>
       </c>
@@ -2011,6 +2017,12 @@
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>48</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
       </c>
       <c r="D41" t="s">
         <v>51</v>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9B06ED-5A53-574D-A7F5-88BFFAF0C326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11923B76-2433-2F48-A4A1-6CA8C9EA27E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2078,6 +2078,12 @@
       <c r="A44" t="s">
         <v>45</v>
       </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
       <c r="D44" t="s">
         <v>47</v>
       </c>
@@ -2092,6 +2098,12 @@
       <c r="A45" t="s">
         <v>50</v>
       </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
       <c r="D45" t="s">
         <v>52</v>
       </c>
@@ -2106,6 +2118,12 @@
       <c r="A46" t="s">
         <v>53</v>
       </c>
+      <c r="B46">
+        <v>5</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
       <c r="D46" t="s">
         <v>56</v>
       </c>
@@ -2120,6 +2138,12 @@
       <c r="A47" t="s">
         <v>58</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
       <c r="D47" t="s">
         <v>61</v>
       </c>
@@ -2134,6 +2158,12 @@
       <c r="A48" t="s">
         <v>55</v>
       </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
       <c r="D48" t="s">
         <v>57</v>
       </c>
@@ -2147,6 +2177,12 @@
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>60</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
       </c>
       <c r="D49" t="s">
         <v>62</v>

--- a/fifa_world_cup_2026_results.xlsx
+++ b/fifa_world_cup_2026_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juan_bohorquez/Documents/repos/world_cup_ampl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11923B76-2433-2F48-A4A1-6CA8C9EA27E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6536E74F-0455-5448-B4C9-9DAE01C4D6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="teams" sheetId="1" r:id="rId1"/>
@@ -2198,6 +2198,12 @@
       <c r="A50" t="s">
         <v>7</v>
       </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
       <c r="D50" t="s">
         <v>3</v>
       </c>
@@ -2212,6 +2218,12 @@
       <c r="A51" t="s">
         <v>5</v>
       </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
       <c r="D51" t="s">
         <v>6</v>
       </c>
@@ -2226,6 +2238,12 @@
       <c r="A52" t="s">
         <v>12</v>
       </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
       <c r="D52" t="s">
         <v>8</v>
       </c>
@@ -2240,6 +2258,12 @@
       <c r="A53" t="s">
         <v>10</v>
       </c>
+      <c r="B53">
+        <v>3</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
       <c r="D53" t="s">
         <v>11</v>
       </c>
@@ -2254,6 +2278,12 @@
       <c r="A54" t="s">
         <v>22</v>
       </c>
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
       <c r="D54" t="s">
         <v>18</v>
       </c>
@@ -2268,6 +2298,12 @@
       <c r="A55" t="s">
         <v>20</v>
       </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
       <c r="D55" t="s">
         <v>21</v>
       </c>
@@ -2282,6 +2318,12 @@
       <c r="A56" t="s">
         <v>17</v>
       </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
       <c r="D56" t="s">
         <v>13</v>
       </c>
@@ -2296,6 +2338,12 @@
       <c r="A57" t="s">
         <v>15</v>
       </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
       <c r="D57" t="s">
         <v>16</v>
       </c>
@@ -2310,6 +2358,12 @@
       <c r="A58" t="s">
         <v>27</v>
       </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
       <c r="D58" t="s">
         <v>23</v>
       </c>
@@ -2324,6 +2378,12 @@
       <c r="A59" t="s">
         <v>25</v>
       </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
       <c r="D59" t="s">
         <v>26</v>
       </c>
@@ -2338,6 +2398,12 @@
       <c r="A60" t="s">
         <v>32</v>
       </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
       <c r="D60" t="s">
         <v>28</v>
       </c>
@@ -2352,6 +2418,12 @@
       <c r="A61" t="s">
         <v>30</v>
       </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
       <c r="D61" t="s">
         <v>31</v>
       </c>
@@ -2366,6 +2438,12 @@
       <c r="A62" t="s">
         <v>37</v>
       </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>5</v>
+      </c>
       <c r="D62" t="s">
         <v>33</v>
       </c>
@@ -2380,6 +2458,12 @@
       <c r="A63" t="s">
         <v>35</v>
       </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
       <c r="D63" t="s">
         <v>36</v>
       </c>
@@ -2394,6 +2478,12 @@
       <c r="A64" t="s">
         <v>42</v>
       </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
       <c r="D64" t="s">
         <v>38</v>
       </c>
@@ -2408,6 +2498,12 @@
       <c r="A65" t="s">
         <v>40</v>
       </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
       <c r="D65" t="s">
         <v>41</v>
       </c>
@@ -2422,6 +2518,12 @@
       <c r="A66" t="s">
         <v>47</v>
       </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>4</v>
+      </c>
       <c r="D66" t="s">
         <v>43</v>
       </c>
@@ -2436,6 +2538,12 @@
       <c r="A67" t="s">
         <v>45</v>
       </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
       <c r="D67" t="s">
         <v>46</v>
       </c>
@@ -2450,6 +2558,12 @@
       <c r="A68" t="s">
         <v>52</v>
       </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
       <c r="D68" t="s">
         <v>48</v>
       </c>
@@ -2464,6 +2578,12 @@
       <c r="A69" t="s">
         <v>50</v>
       </c>
+      <c r="B69">
+        <v>3</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
       <c r="D69" t="s">
         <v>51</v>
       </c>
@@ -2478,6 +2598,12 @@
       <c r="A70" t="s">
         <v>57</v>
       </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
       <c r="D70" t="s">
         <v>53</v>
       </c>
@@ -2492,6 +2618,12 @@
       <c r="A71" t="s">
         <v>55</v>
       </c>
+      <c r="B71">
+        <v>3</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
       <c r="D71" t="s">
         <v>56</v>
       </c>
@@ -2506,6 +2638,12 @@
       <c r="A72" t="s">
         <v>62</v>
       </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
       <c r="D72" t="s">
         <v>58</v>
       </c>
@@ -2519,6 +2657,12 @@
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>60</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
       </c>
       <c r="D73" t="s">
         <v>61</v>
